--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_recovery_screen.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_recovery_screen.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\qiji\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69E8FA5-A717-4B49-B2D7-1F74FBDA3AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_recovery_screen" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -86,7 +90,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -103,7 +107,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>ID</t>
     </r>
@@ -146,7 +150,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -248,7 +252,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Z</t>
     </r>
@@ -256,7 +260,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>0</t>
     </r>
@@ -356,19 +360,23 @@
   </si>
   <si>
     <t>技能</t>
+  </si>
+  <si>
+    <t>3.职业
+5.强化等级
+6.追加等级
+7.幸运属性
+8.装备技能
+9.宝石类型
+11.无视装备提升</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -387,157 +395,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -546,198 +419,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149906918546098"/>
+        <fgColor theme="0" tint="-0.1498764000366222"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -745,253 +438,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1022,66 +473,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="28">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1100,36 +509,227 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
+          <bgColor rgb="FFFF9900"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
         <color theme="1"/>
       </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.39994506668294322"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79995117038483843"/>
+          <bgColor theme="4" tint="0.79995117038483843"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <color theme="1"/>
       </font>
       <border>
@@ -1140,7 +740,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color theme="0"/>
       </font>
       <fill>
@@ -1168,154 +768,40 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
+          <color theme="4" tint="0.39994506668294322"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="totalRow" dxfId="6"/>
-      <tableStyleElement type="firstColumn" dxfId="5"/>
-      <tableStyleElement type="lastColumn" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" dxfId="27"/>
+      <tableStyleElement type="headerRow" dxfId="26"/>
+      <tableStyleElement type="totalRow" dxfId="25"/>
+      <tableStyleElement type="firstColumn" dxfId="24"/>
+      <tableStyleElement type="lastColumn" dxfId="23"/>
+      <tableStyleElement type="firstRowStripe" dxfId="22"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="21"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="18"/>
-      <tableStyleElement type="totalRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
-      <tableStyleElement type="pageFieldValues" dxfId="9"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="totalRow" dxfId="19"/>
+      <tableStyleElement type="firstRowStripe" dxfId="18"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="17"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="16"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="14"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="13"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="12"/>
+      <tableStyleElement type="pageFieldValues" dxfId="11"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1573,27 +1059,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.4571428571429" customWidth="1"/>
-    <col min="3" max="4" width="19.8190476190476" customWidth="1"/>
-    <col min="5" max="6" width="20.5428571428571" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="4" width="19.85546875" customWidth="1"/>
+    <col min="5" max="6" width="20.5703125" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="8" width="33.2666666666667" customWidth="1"/>
-    <col min="9" max="9" width="28.4571428571429" customWidth="1"/>
-    <col min="10" max="10" width="17.2666666666667" customWidth="1"/>
-    <col min="11" max="11" width="26.8190476190476" style="1" customWidth="1"/>
-    <col min="12" max="12" width="20.5428571428571" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.28515625" customWidth="1"/>
+    <col min="9" max="9" width="28.42578125" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="26.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="20.5703125" style="2" customWidth="1"/>
     <col min="13" max="13" width="23" style="2" customWidth="1"/>
-    <col min="14" max="14" width="33.2666666666667" style="2" customWidth="1"/>
+    <col min="14" max="14" width="33.28515625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1640,7 +1126,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" ht="94.5" spans="1:14">
+    <row r="2" spans="1:14" ht="96">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1650,8 +1136,8 @@
       <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>17</v>
+      <c r="D2" s="15" t="s">
+        <v>84</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>17</v>
@@ -2321,7 +1807,7 @@
         <v>1253000599</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="16.5" spans="1:14">
+    <row r="33" spans="1:14" ht="16.5">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -2337,15 +1823,11 @@
       <c r="E33" t="s">
         <v>9</v>
       </c>
-      <c r="J33" s="14">
+      <c r="J33" s="13">
         <v>1254001399</v>
       </c>
-      <c r="K33" s="1"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
-    </row>
-    <row r="34" customFormat="1" ht="16.5" spans="1:14">
+    </row>
+    <row r="34" spans="1:14" ht="16.5">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -2361,15 +1843,11 @@
       <c r="E34" t="s">
         <v>9</v>
       </c>
-      <c r="J34" s="14">
+      <c r="J34" s="13">
         <v>1254001499</v>
       </c>
-      <c r="K34" s="1"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
-    </row>
-    <row r="35" customFormat="1" ht="16.5" spans="1:14">
+    </row>
+    <row r="35" spans="1:14" ht="16.5">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -2379,17 +1857,15 @@
       <c r="C35" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D35"/>
+      <c r="D35">
+        <v>3</v>
+      </c>
       <c r="E35" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J35" s="13"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
-    </row>
-    <row r="36" customFormat="1" ht="16.5" spans="1:14">
+    </row>
+    <row r="36" spans="1:14" ht="16.5">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -2399,17 +1875,15 @@
       <c r="C36" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D36"/>
+      <c r="D36">
+        <v>3</v>
+      </c>
       <c r="E36" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J36" s="15"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
-    </row>
-    <row r="37" customFormat="1" ht="16.5" spans="1:14">
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="1:14" ht="16.5">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -2419,15 +1893,13 @@
       <c r="C37" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D37"/>
+      <c r="D37">
+        <v>3</v>
+      </c>
       <c r="E37" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J37" s="15"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
+      <c r="J37" s="14"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="1">
@@ -2445,7 +1917,7 @@
       <c r="E38" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="N38" s="16" t="s">
+      <c r="N38" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2465,7 +1937,7 @@
       <c r="E39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="N39" s="16" t="s">
+      <c r="N39" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2485,7 +1957,7 @@
       <c r="E40" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="N40" s="16" t="s">
+      <c r="N40" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2501,33 +1973,33 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="J28:J30">
+    <cfRule type="duplicateValues" dxfId="10" priority="28"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J31">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J32">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J33:J34">
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J35">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J36">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J37">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J28:J30">
-    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J33:J34">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_recovery_screen.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_recovery_screen.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\qiji\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B69E8FA5-A717-4B49-B2D7-1F74FBDA3AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_recovery_screen" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="84">
   <si>
     <t>id</t>
   </si>
@@ -90,7 +86,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -107,7 +103,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>ID</t>
     </r>
@@ -150,7 +146,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -252,7 +248,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve"> Z</t>
     </r>
@@ -260,7 +256,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
-        <family val="2"/>
+        <charset val="134"/>
       </rPr>
       <t>0</t>
     </r>
@@ -360,23 +356,19 @@
   </si>
   <si>
     <t>技能</t>
-  </si>
-  <si>
-    <t>3.职业
-5.强化等级
-6.追加等级
-7.幸运属性
-8.装备技能
-9.宝石类型
-11.无视装备提升</t>
-    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -395,22 +387,157 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -419,18 +546,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1498764000366222"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79995117038483843"/>
+        <fgColor theme="0" tint="-0.149906918546098"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -438,11 +745,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -473,24 +1022,66 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="19">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -509,227 +1100,36 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF9900"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -740,7 +1140,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -768,40 +1168,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="27"/>
-      <tableStyleElement type="headerRow" dxfId="26"/>
-      <tableStyleElement type="totalRow" dxfId="25"/>
-      <tableStyleElement type="firstColumn" dxfId="24"/>
-      <tableStyleElement type="lastColumn" dxfId="23"/>
-      <tableStyleElement type="firstRowStripe" dxfId="22"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="21"/>
+      <tableStyleElement type="wholeTable" dxfId="8"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="totalRow" dxfId="6"/>
+      <tableStyleElement type="firstColumn" dxfId="5"/>
+      <tableStyleElement type="lastColumn" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="totalRow" dxfId="19"/>
-      <tableStyleElement type="firstRowStripe" dxfId="18"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="17"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="16"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="14"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="13"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="12"/>
-      <tableStyleElement type="pageFieldValues" dxfId="11"/>
+      <tableStyleElement type="headerRow" dxfId="18"/>
+      <tableStyleElement type="totalRow" dxfId="17"/>
+      <tableStyleElement type="firstRowStripe" dxfId="16"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="14"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="12"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="11"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="10"/>
+      <tableStyleElement type="pageFieldValues" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1059,27 +1573,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:N41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="4" width="19.85546875" customWidth="1"/>
-    <col min="5" max="6" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.4571428571429" customWidth="1"/>
+    <col min="3" max="4" width="19.8190476190476" customWidth="1"/>
+    <col min="5" max="6" width="20.5428571428571" customWidth="1"/>
     <col min="7" max="7" width="23" customWidth="1"/>
-    <col min="8" max="8" width="33.28515625" customWidth="1"/>
-    <col min="9" max="9" width="28.42578125" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
-    <col min="11" max="11" width="26.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="20.5703125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.2666666666667" customWidth="1"/>
+    <col min="9" max="9" width="28.4571428571429" customWidth="1"/>
+    <col min="10" max="10" width="17.2666666666667" customWidth="1"/>
+    <col min="11" max="11" width="26.8190476190476" style="1" customWidth="1"/>
+    <col min="12" max="12" width="20.5428571428571" style="2" customWidth="1"/>
     <col min="13" max="13" width="23" style="2" customWidth="1"/>
-    <col min="14" max="14" width="33.28515625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="33.2666666666667" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1126,7 +1640,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="96">
+    <row r="2" ht="94.5" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1136,8 +1650,8 @@
       <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="15" t="s">
-        <v>84</v>
+      <c r="D2" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>17</v>
@@ -1807,7 +2321,7 @@
         <v>1253000599</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="16.5">
+    <row r="33" customFormat="1" ht="16.5" spans="1:14">
       <c r="A33" s="1">
         <v>29</v>
       </c>
@@ -1823,11 +2337,15 @@
       <c r="E33" t="s">
         <v>9</v>
       </c>
-      <c r="J33" s="13">
+      <c r="J33" s="14">
         <v>1254001399</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" ht="16.5">
+      <c r="K33" s="1"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+    </row>
+    <row r="34" customFormat="1" ht="16.5" spans="1:14">
       <c r="A34" s="1">
         <v>30</v>
       </c>
@@ -1843,11 +2361,15 @@
       <c r="E34" t="s">
         <v>9</v>
       </c>
-      <c r="J34" s="13">
+      <c r="J34" s="14">
         <v>1254001499</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" ht="16.5">
+      <c r="K34" s="1"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+    </row>
+    <row r="35" customFormat="1" ht="16.5" spans="1:14">
       <c r="A35" s="1">
         <v>31</v>
       </c>
@@ -1857,15 +2379,17 @@
       <c r="C35" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D35">
-        <v>3</v>
-      </c>
+      <c r="D35"/>
       <c r="E35" s="3" t="s">
         <v>74</v>
       </c>
       <c r="J35" s="13"/>
-    </row>
-    <row r="36" spans="1:14" ht="16.5">
+      <c r="K35" s="1"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+    </row>
+    <row r="36" customFormat="1" ht="16.5" spans="1:14">
       <c r="A36" s="1">
         <v>32</v>
       </c>
@@ -1875,15 +2399,17 @@
       <c r="C36" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D36">
-        <v>3</v>
-      </c>
+      <c r="D36"/>
       <c r="E36" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J36" s="14"/>
-    </row>
-    <row r="37" spans="1:14" ht="16.5">
+      <c r="J36" s="15"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+    </row>
+    <row r="37" customFormat="1" ht="16.5" spans="1:14">
       <c r="A37" s="1">
         <v>33</v>
       </c>
@@ -1893,13 +2419,15 @@
       <c r="C37" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D37">
-        <v>3</v>
-      </c>
+      <c r="D37"/>
       <c r="E37" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J37" s="14"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="1">
@@ -1917,7 +2445,7 @@
       <c r="E38" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="N38" t="s">
+      <c r="N38" s="16" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1937,7 +2465,7 @@
       <c r="E39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="N39" t="s">
+      <c r="N39" s="16" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1957,7 +2485,7 @@
       <c r="E40" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="N40" t="s">
+      <c r="N40" s="16" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1973,33 +2501,33 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="J28:J30">
-    <cfRule type="duplicateValues" dxfId="10" priority="28"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J31">
-    <cfRule type="duplicateValues" dxfId="9" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J32">
-    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J35">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J36">
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J37">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J28:J30">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J33:J34">
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J35">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J36">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J37">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>